--- a/spreadsheet_codegen/examples/abs_fpi/abs_fpi_internal.xlsx
+++ b/spreadsheet_codegen/examples/abs_fpi/abs_fpi_internal.xlsx
@@ -994,7 +994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1041,7 +1041,7 @@
     <row r="7">
       <c r="A7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">          excel-codegen render -c &lt;配置&gt;.yaml -x abs_fpi_internal.xlsx --write-excel</t>
+          <t xml:space="preserve">          spreadsheet-codegen render -c &lt;配置&gt;.yaml -x abs_fpi_internal.xlsx --write-excel</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
     <row r="10">
       <c r="A10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">      想确认表里的代码是不是已经过期：excel-codegen check -c &lt;配置&gt;.yaml</t>
+          <t xml:space="preserve">      想确认表里的代码是不是已经过期：spreadsheet-codegen check -c &lt;配置&gt;.yaml</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E127"/>
+  <dimension ref="A1:E125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="2" max="2"/>
@@ -4564,8 +4564,6 @@
         <v/>
       </c>
     </row>
-    <row r="126"/>
-    <row r="127"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4577,7 +4575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AE7"/>
+  <dimension ref="A1:AE5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -4612,6 +4610,7 @@
     <col width="160" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="19" t="inlineStr">
         <is>
@@ -5120,8 +5119,6 @@
         <v/>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6864,7 +6861,7 @@
     <row r="174">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>## excel-codegen-meta</t>
+          <t>## spreadsheet-codegen-meta</t>
         </is>
       </c>
     </row>
